--- a/data/METADATA_LIPOLYSIS.xlsx
+++ b/data/METADATA_LIPOLYSIS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carosandovalcab/Documents/GitHub/data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A10ABDAE-418C-384A-BC0A-4CD8FB70B8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD3D799-EEC1-0E40-86F3-FF41C1FE38FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="44800" windowHeight="25200" xr2:uid="{AA7841D1-94ED-6D41-8A64-92E29844A2F4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="24700" xr2:uid="{AA7841D1-94ED-6D41-8A64-92E29844A2F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,19 +124,22 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,241 +496,277 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
         <v>9432</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="5">
         <v>0.09</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="5">
         <v>0.09</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="5">
         <v>73026</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
         <v>9433</v>
       </c>
-      <c r="E3">
-        <v>73126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2">
+        <v>73126</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
         <v>9437</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="5">
         <v>0.11</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="5">
         <v>0.06</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="5">
         <v>0.09</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="5">
         <v>73026</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
         <v>9441</v>
       </c>
-      <c r="E5">
-        <v>73126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2">
+        <v>73126</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
         <v>9449</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="5">
         <v>0.09</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5">
         <v>73026</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
         <v>9451</v>
       </c>
-      <c r="E7">
-        <v>73126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2">
+        <v>73126</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
         <v>9452</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="5">
         <v>0.1</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="5">
         <v>73026</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>9454</v>
       </c>
-      <c r="E9">
-        <v>73126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2">
+        <v>73126</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
         <v>9455</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="5">
         <v>0.06</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2">
+      <c r="D10" s="5"/>
+      <c r="E10" s="5">
         <v>73026</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>9436</v>
       </c>
-      <c r="E11">
-        <v>73126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2">
+        <v>73126</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
         <v>9438</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="5">
         <v>0.09</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="5">
         <v>0.1</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="5">
         <v>0.11</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="5">
         <v>73026</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>9439</v>
       </c>
-      <c r="E13">
-        <v>73126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2">
+        <v>73126</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
         <v>9443</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="5">
         <v>0.13</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="5">
         <v>0.12</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="5">
         <v>0.11</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="5">
         <v>73026</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>9444</v>
       </c>
-      <c r="E15">
-        <v>73126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2">
+        <v>73126</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
         <v>9450</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="5">
         <v>0.06</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="5">
         <v>0.1</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="5">
         <v>0.05</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="5">
         <v>73026</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
         <v>9453</v>
       </c>
-      <c r="E17">
-        <v>73126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2">
+        <v>73126</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
         <v>9456</v>
       </c>
-      <c r="E18">
-        <v>73126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2">
+        <v>73126</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E25" xr:uid="{80E4913D-09D1-AE4B-948B-AADE93EA3F0C}">
     <filterColumn colId="4">
       <filters blank="1">
-        <filter val="73026"/>
+        <filter val="73126"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/METADATA_LIPOLYSIS.xlsx
+++ b/data/METADATA_LIPOLYSIS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carosandovalcab/Documents/GitHub/data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD3D799-EEC1-0E40-86F3-FF41C1FE38FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0D2C9A-2033-0B4F-8653-201827A311C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="24700" xr2:uid="{AA7841D1-94ED-6D41-8A64-92E29844A2F4}"/>
   </bookViews>
@@ -93,7 +93,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -101,45 +101,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,302 +443,340 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E4913D-09D1-AE4B-948B-AADE93EA3F0C}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="6" width="10.83203125" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>9432</v>
       </c>
-      <c r="B2" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="B2" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C2" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D2" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="E2" s="1">
         <v>73026</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>9433</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2">
-        <v>73126</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+      <c r="B3" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>73126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>9437</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="1">
         <v>0.11</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="1">
         <v>0.06</v>
       </c>
-      <c r="D4" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="E4" s="1">
         <v>73026</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>9441</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2">
-        <v>73126</v>
-      </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+      <c r="B5" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>73126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>9449</v>
       </c>
-      <c r="B6" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5">
+      <c r="B6" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="E6" s="1">
         <v>73026</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>9451</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2">
-        <v>73126</v>
-      </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+      <c r="B7" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="E7" s="1">
+        <v>73126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>9452</v>
       </c>
-      <c r="B8" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="1">
         <v>73026</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>9454</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2">
-        <v>73126</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="B9" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>73126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <v>9455</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="1">
         <v>0.06</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5">
+      <c r="E10" s="1">
         <v>73026</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>9436</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2">
-        <v>73126</v>
-      </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="B11" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="E11" s="1">
+        <v>73126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <v>9438</v>
       </c>
-      <c r="B12" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="B12" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="1">
         <v>0.11</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="1">
         <v>73026</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>9439</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2">
-        <v>73126</v>
-      </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="B13" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="E13" s="1">
+        <v>73126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
         <v>9443</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="1">
         <v>0.13</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="1">
         <v>0.12</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="1">
         <v>0.11</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="1">
         <v>73026</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>9444</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2">
-        <v>73126</v>
-      </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+      <c r="B15" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="E15" s="1">
+        <v>73126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
         <v>9450</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="1">
         <v>0.06</v>
       </c>
-      <c r="C16" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D16" s="1">
         <v>0.05</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="1">
         <v>73026</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <v>9453</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2">
-        <v>73126</v>
-      </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+      <c r="B17" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="E17" s="1">
+        <v>73126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
         <v>9456</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2">
-        <v>73126</v>
-      </c>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
+      <c r="B18" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="E18" s="1">
+        <v>73126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E25" xr:uid="{80E4913D-09D1-AE4B-948B-AADE93EA3F0C}">
-    <filterColumn colId="4">
-      <filters blank="1">
-        <filter val="73126"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
